--- a/Trained_xray_model/experiment_results.xlsx
+++ b/Trained_xray_model/experiment_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,38 +442,22 @@
           <t>Run2_Val</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Run3_Train</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Run3_Val</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0246</v>
+        <v>0.0229</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0095</v>
+        <v>0.0045</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0061</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.0045</v>
+        <v>0.0044</v>
       </c>
     </row>
     <row r="3">
@@ -481,22 +465,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0157</v>
+        <v>0.0143</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0108</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0061</v>
+        <v>0.0044</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0053</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.0049</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.0044</v>
+        <v>0.0039</v>
       </c>
     </row>
     <row r="4">
@@ -504,22 +482,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0104</v>
+        <v>0.0077</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0083</v>
+        <v>0.0067</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0053</v>
+        <v>0.0046</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.0046</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.0044</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="5">
@@ -527,22 +499,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0095</v>
+        <v>0.0062</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0054</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0054</v>
+        <v>0.0038</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.0044</v>
+        <v>0.0039</v>
       </c>
     </row>
     <row r="6">
@@ -550,22 +516,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0083</v>
+        <v>0.0056</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007</v>
+        <v>0.0047</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0054</v>
+        <v>0.0043</v>
       </c>
       <c r="E6" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.0045</v>
+        <v>0.0038</v>
       </c>
     </row>
     <row r="7">
@@ -573,22 +533,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0076</v>
+        <v>0.0055</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0069</v>
+        <v>0.0052</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0053</v>
+        <v>0.0039</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0051</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.0044</v>
+        <v>0.0038</v>
       </c>
     </row>
     <row r="8">
@@ -596,22 +550,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0073</v>
+        <v>0.005</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0066</v>
+        <v>0.0044</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0054</v>
+        <v>0.0044</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0049</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.0053</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.0044</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="9">
@@ -619,22 +567,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0071</v>
+        <v>0.0047</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0058</v>
+        <v>0.0042</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0057</v>
+        <v>0.0041</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0047</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.0045</v>
+        <v>0.0038</v>
       </c>
     </row>
     <row r="10">
@@ -642,22 +584,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0067</v>
+        <v>0.0048</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0057</v>
+        <v>0.0047</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0055</v>
+        <v>0.0043</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0046</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.0053</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.0044</v>
+        <v>0.0037</v>
       </c>
     </row>
     <row r="11">
@@ -665,22 +601,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0065</v>
+        <v>0.0046</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0056</v>
+        <v>0.004</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0053</v>
+        <v>0.0038</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0047</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.0044</v>
+        <v>0.0037</v>
       </c>
     </row>
   </sheetData>
